--- a/dungeon_monster_cards.xlsx
+++ b/dungeon_monster_cards.xlsx
@@ -33,7 +33,7 @@
     <t>Gash</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 1 Damage to each Adventurer.</t>
+    <t xml:space="preserve">Deal 2 Damage to each Adventurer.</t>
   </si>
   <si>
     <t>cardimages/darkness.png</t>
@@ -42,7 +42,7 @@
     <t>Darkness</t>
   </si>
   <si>
-    <t xml:space="preserve">Prevent 1 Damage for each Adventurer in the party.</t>
+    <t xml:space="preserve">Prevent 2 Damage for each Adventurer in the party.</t>
   </si>
   <si>
     <t>cardimages/mimic.png</t>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Rotting Corpse</t>
   </si>
   <si>
-    <t xml:space="preserve">If you Gather this turn, take 2 Damage.</t>
+    <t xml:space="preserve">If you Gather this turn, take 4 Damage.</t>
   </si>
   <si>
     <t>cardimages/rusty_metal.png</t>
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Rusty Metal</t>
   </si>
   <si>
-    <t xml:space="preserve">Each Adventurer must take 1 Damage and lose a resource if able.</t>
+    <t xml:space="preserve">Each Adventurer must take 2 Damage and lose a resource if able.</t>
   </si>
   <si>
     <t>cardimages/suspicious_goo.png</t>
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Spike Trap</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 2 Damage to each Adventurer.</t>
+    <t xml:space="preserve">Deal 4 Damage to each Adventurer.</t>
   </si>
   <si>
     <t>cardimages/rolling_boulder.png</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Rolling Boulder</t>
   </si>
   <si>
-    <t xml:space="preserve">Deal 1 Damage to each Adventurer; if any took unprevented damage, they take +2 Damage.</t>
+    <t xml:space="preserve">Deal 2 Damage to each Adventurer; if any took unprevented damage, they take +4 Damage.</t>
   </si>
   <si>
     <t>cardimages/treasure_trove.png</t>
